--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/INDIANA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/INDIANA_2020.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Praxedis G. Guerero</t>
+          <t>Praxedis G. Guerrero</t>
         </is>
       </c>
       <c r="C93">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C140">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C159">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C207">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C232">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C241">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C249">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C333">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C379">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C462">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C647">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C681">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C682">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C708">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C819">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C883">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1034">
